--- a/stories/arbres/ATOM-SEC.MAI.002-02.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ulysse est dans la cuisine. Papa coupe des pommes. Un petit pot fermé est là. Ulysse ne le connaît pas. C'est de l'inconnu. Ulysse a envie de goûter. Il va vers papa. Il dit : papa, je peux. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Papa prend le pot. Papa dit : c'est du miel. Tu peux goûter. Ulysse goûte une petite cuillère. C'est sucré. Papa dit : on demande à un adulte.</t>
+          <t>Ulysse est dans la cuisine. Papa coupe des pommes. Un petit pot fermé est là. Ulysse ne le connaît pas. C'est de l'inconnu. Ulysse a envie de goûter. Il va vers papa. Papa, je peux. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Papa prend le pot. C'est du miel. Tu peux goûter. Ulysse goûte une petite cuillère. C'est sucré. On demande à un adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Ulysse est dans la cuisine. Papa coupe des pommes. Un petit pot fermé est là. Ulysse ne le connaît pas. C'est de l'inconnu. Ulysse a envie de goûter. Il va vers papa.
+narrateur|Papa, je peux. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Papa prend le pot.
+papa|C'est du miel. Tu peux goûter.
+narrateur|Ulysse goûte une petite cuillère. C'est sucré.
+papa|On demande à un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1473,6 +1498,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Ulysse voit un pot inconnu. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1645,6 +1675,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Ulysse a demandé. L'adulte a répondu. Le petit pot est du miel.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1842,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Ulysse boit une gorgée d'eau. Papa range le pot.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2009,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2049,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.002-02.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 papa|On demande à un adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1505,6 +1511,7 @@
           <t>narrateur|Ulysse voit un pot inconnu. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1680,6 +1687,7 @@
           <t>narrateur|Ulysse a demandé. L'adulte a répondu. Le petit pot est du miel.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1847,6 +1855,7 @@
           <t>narrateur|Ulysse boit une gorgée d'eau. Papa range le pot.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2014,6 +2023,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2032,7 +2042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2056,6 +2066,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2070,7 +2094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2257,6 +2281,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.MAI.002-02.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ulysse demande à papa</t>
+          <t>Le miel de Victorino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Les bottes sèchent près de la porte. Victorino voit un petit pot. Il demande à papa. C'est du miel. Il goûte.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ulysse est dans la cuisine. Papa coupe des pommes. Un petit pot fermé est là. Ulysse ne le connaît pas. C'est de l'inconnu. Ulysse a envie de goûter. Il va vers papa. Papa, je peux. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Papa prend le pot. C'est du miel. Tu peux goûter. Ulysse goûte une petite cuillère. C'est sucré. On demande à un adulte.</t>
+          <t>Près de la porte, les bottes sont encore mouillées. Une goutte tombe sur le carreau. L'horloge jaune fait tic. Ça sent la pomme coupée. Victorino, tu as vu tes bottes ? Oui, papa. Elles sont mouillées. Elles sèchent. C'est bien. La maison sent la pomme. Un oiseau chante derrière la vitre. Tu as entendu l'oiseau ? Oui, papa. Il chante. Il chante pour nous. Papa coupe des pommes. Les morceaux sont blancs et lisses. Ils tombent dans l'assiette ronde. En ce moment, Victorino est près de la table. La table est un peu froide. Un petit pot fermé est là. Victorino ne le connaît pas. C'est de l'inconnu. Victorino a envie de goûter. Il pose les mains sur ses genoux. Il va vers papa. Papa, je peux ? Tu demandes. Bravo. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Papa prend le pot. C'est du miel. Tu peux goûter. Victorino prend une petite cuillère. Il goûte une petite cuillère. C'est sucré. C'est sucré, papa. Oui. Parce que tu as demandé. On demande à un adulte. Bravo, Victorino. Victorino pose la cuillère. Tu as fini de goûter ? Oui, papa. Bravo. Tu as fait du bon travail. L'horloge jaune fait encore tic. Une goutte brille près des bottes. L'oiseau chante encore. Tes mains étaient sur tes genoux ? Oui, papa. Bravo.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,55 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Ulysse est dans la cuisine. Papa coupe des pommes. Un petit pot fermé est là. Ulysse ne le connaît pas. C'est de l'inconnu. Ulysse a envie de goûter. Il va vers papa.
-narrateur|Papa, je peux. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Papa prend le pot.
-papa|C'est du miel. Tu peux goûter.
-narrateur|Ulysse goûte une petite cuillère. C'est sucré.
-papa|On demande à un adulte.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Près de la porte, les bottes sont encore mouillées.
+narrateur|Une goutte tombe sur le carreau.
+narrateur|L'horloge jaune fait tic.
+narrateur|Ça sent la pomme coupée.
+papa|Victorino, tu as vu tes bottes ?
+enfant-m|Oui, papa. Elles sont mouillées.
+papa|Elles sèchent. C'est bien.
+narrateur|La maison sent la pomme.
+narrateur|Un oiseau chante derrière la vitre.
+papa|Tu as entendu l'oiseau ?
+enfant-m|Oui, papa. Il chante.
+papa|Il chante pour nous.
+narrateur|Papa coupe des pommes.
+narrateur|Les morceaux sont blancs et lisses.
+narrateur|Ils tombent dans l'assiette ronde.
+narrateur|En ce moment, Victorino est près de la table.
+narrateur|La table est un peu froide.
+narrateur|Un petit pot fermé est là.
+narrateur|Victorino ne le connaît pas.
+narrateur|C'est de l'inconnu.
+narrateur|Victorino a envie de goûter.
+narrateur|Il pose les mains sur ses genoux.
+narrateur|Il va vers papa.
+enfant-m|Papa, je peux ?
+papa|Tu demandes. Bravo.
+narrateur|Avant de goûter l'inconnu, on demande.
+narrateur|On demande à l'adulte.
+narrateur|Papa prend le pot.
+papa|C'est du miel.
+papa|Tu peux goûter.
+narrateur|Victorino prend une petite cuillère.
+narrateur|Il goûte une petite cuillère.
+narrateur|C'est sucré.
+enfant-m|C'est sucré, papa.
+papa|Oui. Parce que tu as demandé.
+papa|On demande à un adulte.
+papa|Bravo, Victorino.
+narrateur|Victorino pose la cuillère.
+papa|Tu as fini de goûter ?
+enfant-m|Oui, papa.
+papa|Bravo. Tu as fait du bon travail.
+narrateur|L'horloge jaune fait encore tic.
+narrateur|Une goutte brille près des bottes.
+narrateur|L'oiseau chante encore.
+papa|Tes mains étaient sur tes genoux ?
+enfant-m|Oui, papa.
+papa|Bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1397,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Ulysse voit un pot inconnu. Que fait-il ?</t>
+          <t>Victorino voit un pot inconnu. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1508,10 +1561,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Ulysse voit un pot inconnu. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Victorino voit un pot inconnu.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1536,7 +1589,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Ulysse a demandé. L'adulte a répondu. Le petit pot est du miel.</t>
+          <t>Victorino a demandé. L'adulte a répondu. Le petit pot est du miel. Tu as demandé à papa ? Oui. Bravo. On demande à un adulte. Ça sent encore la pomme. Les bottes sèchent toujours. L'assiette ronde est près de papa. Les pommes sont prêtes ? Oui, papa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1684,10 +1737,20 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Ulysse a demandé. L'adulte a répondu. Le petit pot est du miel.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Victorino a demandé.
+narrateur|L'adulte a répondu.
+narrateur|Le petit pot est du miel.
+papa|Tu as demandé à papa ?
+enfant-m|Oui.
+papa|Bravo.
+papa|On demande à un adulte.
+narrateur|Ça sent encore la pomme.
+narrateur|Les bottes sèchent toujours.
+narrateur|L'assiette ronde est près de papa.
+papa|Les pommes sont prêtes ?
+enfant-m|Oui, papa.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1712,7 +1775,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ulysse boit une gorgée d'eau. Papa range le pot.</t>
+          <t>Victorino boit une gorgée d'eau. L'eau est fraîche. Le pot est rangé ? Oui, papa. Bravo. Tu as fait du bon travail. Papa range le pot. L'horloge jaune fait tic. Les bottes sont encore près de la porte. On goûte une pomme ? Oui, papa. Papa donne un morceau blanc. Victorino croque. C'est doux.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1852,10 +1915,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Ulysse boit une gorgée d'eau. Papa range le pot.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Victorino boit une gorgée d'eau.
+narrateur|L'eau est fraîche.
+papa|Le pot est rangé ?
+enfant-m|Oui, papa.
+papa|Bravo. Tu as fait du bon travail.
+narrateur|Papa range le pot.
+narrateur|L'horloge jaune fait tic.
+narrateur|Les bottes sont encore près de la porte.
+papa|On goûte une pomme ?
+enfant-m|Oui, papa.
+narrateur|Papa donne un morceau blanc.
+narrateur|Victorino croque.
+narrateur|C'est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1880,7 +1954,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Victorino a vu un pot inconnu. Il a demandé à papa. C'était du miel. Bravo, Victorino. C'était sucré. Tu as demandé. Bravo. Les bottes sèchent encore. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2020,10 +2094,16 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Victorino a vu un pot inconnu.
+narrateur|Il a demandé à papa.
+narrateur|C'était du miel.
+papa|Bravo, Victorino.
+enfant-m|C'était sucré.
+papa|Tu as demandé. Bravo.
+narrateur|Les bottes sèchent encore.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2042,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2080,6 +2160,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.002-02.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-02.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Près de la porte, les bottes sont encore mouillées. Une goutte tombe sur le carreau. L'horloge jaune fait tic. Ça sent la pomme coupée. Victorino, tu as vu tes bottes ? Oui, papa. Elles sont mouillées. Elles sèchent. C'est bien. La maison sent la pomme. Un oiseau chante derrière la vitre. Tu as entendu l'oiseau ? Oui, papa. Il chante. Il chante pour nous. Papa coupe des pommes. Les morceaux sont blancs et lisses. Ils tombent dans l'assiette ronde. En ce moment, Victorino est près de la table. La table est un peu froide. Un petit pot fermé est là. Victorino ne le connaît pas. C'est de l'inconnu. Victorino a envie de goûter. Il pose les mains sur ses genoux. Il va vers papa. Papa, je peux ? Tu demandes. Bravo. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Papa prend le pot. C'est du miel. Tu peux goûter. Victorino prend une petite cuillère. Il goûte une petite cuillère. C'est sucré. C'est sucré, papa. Oui. Parce que tu as demandé. On demande à un adulte. Bravo, Victorino. Victorino pose la cuillère. Tu as fini de goûter ? Oui, papa. Bravo. Tu as fait du bon travail. L'horloge jaune fait encore tic. Une goutte brille près des bottes. L'oiseau chante encore. Tes mains étaient sur tes genoux ? Oui, papa. Bravo.</t>
+          <t>Près de la porte, les bottes sont encore mouillées. Une goutte tombe sur le carreau. L'horloge jaune fait tic. Ça sent la pomme coupée. Victorino, tu as vu tes bottes ? Oui, papa. Elles sont mouillées. Elles sèchent. C'est bien. La maison sent la pomme. Un oiseau chante derrière la vitre. Tu as entendu l'oiseau ? Oui, papa. Il chante. Il chante pour nous. Papa coupe des pommes. Les morceaux sont blancs et lisses. Ils tombent dans l'assiette ronde. En ce moment, Victorino est près de la table. La table est un peu froide. Un petit pot fermé est là. Victorino ne le connaît pas. C'est de l'inconnu. Victorino a envie de goûter. Il pose les mains sur ses genoux. Il va vers papa. Papa, je peux ? Tu demandes. Bravo. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Papa prend le pot. C'est du miel. Tu peux goûter. Victorino prend une petite cuillère. Il goûte une petite cuillère. C'est sucré. C'est sucré, papa. Oui. Parce que tu as demandé. On demande à un adulte. Bravo, Victorino. Victorino pose la cuillère. Tu as fini de goûter ? Oui, papa. L'horloge jaune fait encore tic. Une goutte brille près des bottes. L'oiseau chante encore. Tes mains étaient sur tes genoux ? Oui, papa. Bravo.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Ulysse est dans la cuisine. Papa coupe des pommes. Un petit pot fermé est là. Ulysse ne le connaît pas. C'est de l'&lt;emphasis level="moderate"&gt;inconnu&lt;/emphasis&gt;. Ulysse a envie de goûter. Il va vers papa. Il dit : papa, je peux. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Papa prend le pot. Papa dit : c'est du miel. Tu peux goûter. Ulysse goûte une petite cuillère. C'est sucré. Papa dit : on demande à un adulte.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Près de la porte, les bottes sont encore mouillées. Une goutte tombe sur le carreau. L'horloge jaune fait tic. Ça sent la pomme coupée. Victorino, tu as vu tes bottes ? Oui, papa. Elles sont mouillées. Elles sèchent. C'est bien. La maison sent la pomme. Un oiseau chante derrière la vitre. Tu as entendu l'oiseau ? Oui, papa. Il chante. Il chante pour nous. Papa coupe des pommes. Les morceaux sont blancs et lisses. Ils tombent dans l'assiette ronde. En ce moment, Victorino est près de la table. La table est un peu froide. Un petit pot fermé est là. Victorino ne le connaît pas. C'est de l'inconnu. Victorino a envie de goûter. Il pose les mains sur ses genoux. Il va vers papa. Papa, je peux ? Tu demandes. Bravo. Avant de goûter l'inconnu, on demande. On demande à l'adulte. Papa prend le pot. C'est du miel. Tu peux goûter. Victorino prend une petite cuillère. Il goûte une petite cuillère. C'est sucré. C'est sucré, papa. Oui. Parce que tu as demandé. On demande à un adulte. Bravo, Victorino. Victorino pose la cuillère. Tu as fini de goûter ? Oui, papa. L'horloge jaune fait encore tic. Une goutte brille près des bottes. L'oiseau chante encore. Tes mains étaient sur tes genoux ? Oui, papa. Bravo.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1364,7 +1364,6 @@
 narrateur|Victorino pose la cuillère.
 papa|Tu as fini de goûter ?
 enfant-m|Oui, papa.
-papa|Bravo. Tu as fait du bon travail.
 narrateur|L'horloge jaune fait encore tic.
 narrateur|Une goutte brille près des bottes.
 narrateur|L'oiseau chante encore.
@@ -1402,7 +1401,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Ulysse voit un pot &lt;emphasis level="moderate"&gt;inconnu&lt;/emphasis&gt;. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino voit un pot inconnu. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1594,7 +1593,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Ulysse a demandé. L'&lt;emphasis level="moderate"&gt;adulte&lt;/emphasis&gt; a répondu. Le petit pot est du miel.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino a demandé. L'adulte a répondu. Le petit pot est du miel. Tu as demandé à papa ? Oui. Bravo. On demande à un adulte. Ça sent encore la pomme. Les bottes sèchent toujours. L'assiette ronde est près de papa. Les pommes sont prêtes ? Oui, papa.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1775,12 +1774,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Victorino boit une gorgée d'eau. L'eau est fraîche. Le pot est rangé ? Oui, papa. Bravo. Tu as fait du bon travail. Papa range le pot. L'horloge jaune fait tic. Les bottes sont encore près de la porte. On goûte une pomme ? Oui, papa. Papa donne un morceau blanc. Victorino croque. C'est doux.</t>
+          <t>Victorino boit une gorgée d'eau. L'eau est fraîche. Le pot est rangé ? Oui, papa. Papa range le pot. L'horloge jaune fait tic. Les bottes sont encore près de la porte. On goûte une pomme ? Oui, papa. Papa donne un morceau blanc. Victorino croque. C'est doux.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Ulysse boit une gorgée d'eau. Papa range le pot.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino boit une gorgée d'eau. L'eau est fraîche. Le pot est rangé ? Oui, papa. Papa range le pot. L'horloge jaune fait tic. Les bottes sont encore près de la porte. On goûte une pomme ? Oui, papa. Papa donne un morceau blanc. Victorino croque. C'est doux.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1919,7 +1918,6 @@
 narrateur|L'eau est fraîche.
 papa|Le pot est rangé ?
 enfant-m|Oui, papa.
-papa|Bravo. Tu as fait du bon travail.
 narrateur|Papa range le pot.
 narrateur|L'horloge jaune fait tic.
 narrateur|Les bottes sont encore près de la porte.
@@ -1954,12 +1952,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Victorino a vu un pot inconnu. Il a demandé à papa. C'était du miel. Bravo, Victorino. C'était sucré. Tu as demandé. Bravo. Les bottes sèchent encore. L'histoire est finie.</t>
+          <t>Victorino a vu un pot inconnu. Il a demandé à papa. C'était du miel. Bravo, Victorino. C'était sucré. Tu as demandé. Bravo. Les bottes sèchent encore.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino a vu un pot inconnu. Il a demandé à papa. C'était du miel. Bravo, Victorino. C'était sucré. Tu as demandé. Bravo. Les bottes sèchent encore.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2100,8 +2098,7 @@
 papa|Bravo, Victorino.
 enfant-m|C'était sucré.
 papa|Tu as demandé. Bravo.
-narrateur|Les bottes sèchent encore.
-narrateur|L'histoire est finie.</t>
+narrateur|Les bottes sèchent encore.</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2167,6 +2164,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.002-02.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.002-02.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ulysse, papa</t>
+          <t>Victorino, papa</t>
         </is>
       </c>
     </row>
